--- a/dealerlist.xlsx
+++ b/dealerlist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,10 +459,8 @@
           <t>Adelaide North</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150861</t>
-        </is>
+      <c r="B2" t="n">
+        <v>150861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -494,10 +492,8 @@
           <t>Albury Wodonga</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>136901</t>
-        </is>
+      <c r="B3" t="n">
+        <v>136901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -529,10 +525,8 @@
           <t>Ballarat</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>133501</t>
-        </is>
+      <c r="B4" t="n">
+        <v>133501</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -564,10 +558,8 @@
           <t>Bendigo</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>135501</t>
-        </is>
+      <c r="B5" t="n">
+        <v>135501</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -599,10 +591,8 @@
           <t>Blacktown</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>121481</t>
-        </is>
+      <c r="B6" t="n">
+        <v>121481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -634,10 +624,8 @@
           <t>Bunbury</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>162301</t>
-        </is>
+      <c r="B7" t="n">
+        <v>162301</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -669,10 +657,8 @@
           <t>Bundaberg</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>146701</t>
-        </is>
+      <c r="B8" t="n">
+        <v>146701</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -704,10 +690,8 @@
           <t>Bundoora</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>130831</t>
-        </is>
+      <c r="B9" t="n">
+        <v>130831</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -739,10 +723,8 @@
           <t>Cairns</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>148701</t>
-        </is>
+      <c r="B10" t="n">
+        <v>148701</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -770,10 +752,8 @@
           <t>Capalaba</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>141571</t>
-        </is>
+      <c r="B11" t="n">
+        <v>141571</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -805,10 +785,8 @@
           <t>Coffs Harbour</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>124501</t>
-        </is>
+      <c r="B12" t="n">
+        <v>124501</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -840,10 +818,8 @@
           <t>Dubbo</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>128301</t>
-        </is>
+      <c r="B13" t="n">
+        <v>128301</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -875,10 +851,8 @@
           <t>Frankston</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>131991</t>
-        </is>
+      <c r="B14" t="n">
+        <v>131991</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -902,10 +876,8 @@
           <t>Gawler</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>151181</t>
-        </is>
+      <c r="B15" t="n">
+        <v>151181</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -937,10 +909,8 @@
           <t>Gold Coast</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>142141</t>
-        </is>
+      <c r="B16" t="n">
+        <v>142141</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -972,10 +942,8 @@
           <t>Gosford (Wyoming)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>122501</t>
-        </is>
+      <c r="B17" t="n">
+        <v>122501</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -999,10 +967,8 @@
           <t>Gympie</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>145701</t>
-        </is>
+      <c r="B18" t="n">
+        <v>145701</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1034,10 +1000,8 @@
           <t>Hervey Bay</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>146551</t>
-        </is>
+      <c r="B19" t="n">
+        <v>146551</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1069,10 +1033,8 @@
           <t>Hillcrest</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>141181</t>
-        </is>
+      <c r="B20" t="n">
+        <v>141181</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1104,10 +1066,8 @@
           <t>Ipswich</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>143051</t>
-        </is>
+      <c r="B21" t="n">
+        <v>143051</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1158,10 +1118,8 @@
           <t>JAC Motors Campbelltown</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>125601</t>
-        </is>
+      <c r="B23" t="n">
+        <v>125601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1189,10 +1147,8 @@
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>121701</t>
-        </is>
+      <c r="B24" t="n">
+        <v>121701</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1224,10 +1180,8 @@
           <t>Maroochydore</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>145581</t>
-        </is>
+      <c r="B25" t="n">
+        <v>145581</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1259,10 +1213,8 @@
           <t>Mascot</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>120201</t>
-        </is>
+      <c r="B26" t="n">
+        <v>120201</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1294,10 +1246,8 @@
           <t>Mildura</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>135001</t>
-        </is>
+      <c r="B27" t="n">
+        <v>135001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1329,10 +1279,8 @@
           <t>Morayfield</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>145061</t>
-        </is>
+      <c r="B28" t="n">
+        <v>145061</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1364,10 +1312,8 @@
           <t>Nambour</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>145601</t>
-        </is>
+      <c r="B29" t="n">
+        <v>145601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1399,10 +1345,8 @@
           <t>Newcastle</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>122851</t>
-        </is>
+      <c r="B30" t="n">
+        <v>122851</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1430,10 +1374,8 @@
           <t>Nowra</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>125411</t>
-        </is>
+      <c r="B31" t="n">
+        <v>125411</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1465,10 +1407,8 @@
           <t>Orange</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>128001</t>
-        </is>
+      <c r="B32" t="n">
+        <v>128001</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1500,10 +1440,8 @@
           <t>Pakenham</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>138101</t>
-        </is>
+      <c r="B33" t="n">
+        <v>138101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1527,10 +1465,8 @@
           <t>Penrith</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>127501</t>
-        </is>
+      <c r="B34" t="n">
+        <v>127501</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1562,10 +1498,8 @@
           <t>Perth - Maddington</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>161091</t>
-        </is>
+      <c r="B35" t="n">
+        <v>161091</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1589,10 +1523,8 @@
           <t>Perth - Midland</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>160561</t>
-        </is>
+      <c r="B36" t="n">
+        <v>160561</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1624,10 +1556,8 @@
           <t>Perth - VicPark</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>161001</t>
-        </is>
+      <c r="B37" t="n">
+        <v>161001</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1659,10 +1589,8 @@
           <t>Perth - Wanneroo</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>160651</t>
-        </is>
+      <c r="B38" t="n">
+        <v>160651</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1694,10 +1622,8 @@
           <t>Queanbeyan</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>126201</t>
-        </is>
+      <c r="B39" t="n">
+        <v>126201</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1729,10 +1655,8 @@
           <t>Redcliffe</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>140211</t>
-        </is>
+      <c r="B40" t="n">
+        <v>140211</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1764,10 +1688,8 @@
           <t>Rockhampton</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>147001</t>
-        </is>
+      <c r="B41" t="n">
+        <v>147001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1796,22 +1718,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rothwell</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>140221</t>
-        </is>
+          <t>Shepparton</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>136301</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Southern</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1821,7 +1741,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rothwell</t>
+          <t>Shepparton</t>
         </is>
       </c>
       <c r="G42" t="b">
@@ -1831,22 +1751,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Shepparton</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>136301</t>
-        </is>
+          <t>Springwood</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>141271</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>QLD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Northern</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1856,7 +1774,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shepparton</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="G43" t="b">
@@ -1866,22 +1784,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Springwood</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>141271</t>
-        </is>
+          <t>Tamworth</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>123401</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>NSW</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1891,7 +1807,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="G44" t="b">
@@ -1901,34 +1817,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tamworth</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>123401</t>
-        </is>
+          <t>Toowoomba</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>143501</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NSW</t>
+          <t>QLD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>Northern</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tamworth</t>
-        </is>
-      </c>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="b">
         <v>1</v>
       </c>
@@ -1936,13 +1846,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Toowoomba</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>143501</t>
-        </is>
+          <t>Townsville</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>148141</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1967,30 +1875,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Townsville</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>148141</t>
-        </is>
+          <t>Tuggerah</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>122591</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>NSW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tuggerah</t>
+        </is>
+      </c>
       <c r="G47" t="b">
         <v>1</v>
       </c>
@@ -1998,13 +1908,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>122591</t>
-        </is>
+          <t>Tweed Heads</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>124861</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2013,7 +1921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>Northern</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2023,7 +1931,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
+          <t>Tweed</t>
         </is>
       </c>
       <c r="G48" t="b">
@@ -2033,13 +1941,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tweed Heads</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>124861</t>
-        </is>
+          <t>Wagga Wagga</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>126501</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2048,19 +1954,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tweed</t>
-        </is>
-      </c>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="b">
         <v>1</v>
       </c>
@@ -2068,30 +1970,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wagga Wagga</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>126501</t>
-        </is>
+          <t>Warrnambool</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>132801</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NSW</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Eastern</t>
-        </is>
-      </c>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Warrnambool</t>
+        </is>
+      </c>
       <c r="G50" t="b">
         <v>1</v>
       </c>
@@ -2099,20 +1999,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Warrnambool</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>132801</t>
-        </is>
+          <t>Werribee</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>130291</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Southern</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>Active</t>
@@ -2120,45 +2022,10 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Warrnambool</t>
+          <t>Werribee</t>
         </is>
       </c>
       <c r="G51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Werribee</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>130291</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>VIC</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Southern</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Werribee</t>
-        </is>
-      </c>
-      <c r="G52" t="b">
         <v>1</v>
       </c>
     </row>
